--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.59676078662932</v>
+        <v>2.859473627827265</v>
       </c>
       <c r="D2" t="n">
-        <v>17.87483347219725</v>
+        <v>2.904660439232054</v>
       </c>
       <c r="E2" t="n">
-        <v>15.50252596306242</v>
+        <v>2.519160468997642</v>
       </c>
       <c r="F2" t="n">
-        <v>15.42137922976059</v>
+        <v>2.505974124836095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.66212406293923</v>
+        <v>6.607595160227625</v>
       </c>
       <c r="D3" t="n">
-        <v>40.93833958953893</v>
+        <v>6.652480183300076</v>
       </c>
       <c r="E3" t="n">
-        <v>15.50252596306242</v>
+        <v>2.519160468997642</v>
       </c>
       <c r="F3" t="n">
-        <v>15.42137922976059</v>
+        <v>2.505974124836095</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.25355318971368</v>
+        <v>8.978702393328472</v>
       </c>
       <c r="D4" t="n">
-        <v>55.31491014023961</v>
+        <v>8.988672897788938</v>
       </c>
       <c r="E4" t="n">
-        <v>15.50252596306242</v>
+        <v>2.519160468997642</v>
       </c>
       <c r="F4" t="n">
-        <v>15.42137922976059</v>
+        <v>2.505974124836095</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
